--- a/uploads/meta.xlsx
+++ b/uploads/meta.xlsx
@@ -503,7 +503,7 @@
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v/>
+        <v>tree.glb</v>
       </c>
       <c r="B7" t="str">
         <v>Tree (1)</v>

--- a/uploads/meta.xlsx
+++ b/uploads/meta.xlsx
@@ -503,7 +503,7 @@
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>tree.glb</v>
+        <v/>
       </c>
       <c r="B7" t="str">
         <v>Tree (1)</v>
